--- a/docs/data/jp/xlsx/5959.xlsx
+++ b/docs/data/jp/xlsx/5959.xlsx
@@ -7896,7 +7896,7 @@
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Scrap NOI</t>
+          <t>스크랩 매각 수입</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
@@ -8642,7 +8642,7 @@
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>Reversal Of Provision For Loss On Liquidation Of Subsidiaries And Affiliates EI</t>
+          <t>관계회사 정리 손실 충당금 환입액</t>
         </is>
       </c>
       <c r="C111" s="22" t="n">
@@ -8667,7 +8667,7 @@
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>Previous Year Customs Refund Amount EI</t>
+          <t>과년도 관세 환급액</t>
         </is>
       </c>
       <c r="C112" s="22" t="n">
@@ -8934,7 +8934,7 @@
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>Litigation Related Expenses And Other EL</t>
+          <t>소송 등 관련 비용</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -11058,7 +11058,7 @@
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>Loss On Closing Of Factory Ope CF</t>
+          <t>공장 폐쇄 손실</t>
         </is>
       </c>
       <c r="P163" s="22" t="n">
@@ -11239,7 +11239,7 @@
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>Amount Of Customs Refund For The Past Fiscal Year Ope CF</t>
+          <t>과년도 관세 환급액</t>
         </is>
       </c>
       <c r="C170" s="22" t="n">
@@ -11264,7 +11264,7 @@
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>Litigation Related Expenses And Other Ope CF</t>
+          <t>소송 등 관련 비용</t>
         </is>
       </c>
       <c r="C171" s="22" t="n">
@@ -11855,7 +11855,7 @@
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>Payments For Environmental Expenses Ope CF</t>
+          <t>환경 대책비 지급액</t>
         </is>
       </c>
       <c r="R186" s="22" t="n">
@@ -11874,7 +11874,7 @@
     <row r="187">
       <c r="A187" s="20" t="inlineStr">
         <is>
-          <t>Loss On Closing Factory Paid Ope CF</t>
+          <t>공장 폐쇄 손실 지급액</t>
         </is>
       </c>
       <c r="P187" s="22" t="n">
@@ -11943,7 +11943,7 @@
     <row r="190">
       <c r="A190" s="20" t="inlineStr">
         <is>
-          <t>Payment Amount Of Litigation Related Expenses And Other Ope CF</t>
+          <t>소송 등 관련 비용 지급액</t>
         </is>
       </c>
       <c r="C190" s="22" t="n">
@@ -11968,7 +11968,7 @@
     <row r="191">
       <c r="A191" s="20" t="inlineStr">
         <is>
-          <t>Amount Of Customs Refund For The Previous Year Ope CF</t>
+          <t>과년도 관세 환급액</t>
         </is>
       </c>
       <c r="C191" s="22" t="n">
@@ -12629,7 +12629,7 @@
     <row r="213">
       <c r="A213" s="20" t="inlineStr">
         <is>
-          <t>Payments Into Long Term Deposits Paid Inv CF</t>
+          <t>장기 예치금 예입 지출</t>
         </is>
       </c>
       <c r="O213" s="22" t="n">
@@ -12642,7 +12642,7 @@
     <row r="214">
       <c r="A214" s="20" t="inlineStr">
         <is>
-          <t>Collection Of Long Term Deposits Inv CF</t>
+          <t>장기 예치금 회수 수입</t>
         </is>
       </c>
       <c r="P214" s="22" t="n">
